--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4545454545454545</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="B2">
-        <v>0.05405405405405406</v>
+        <v>0.01886792452830189</v>
       </c>
       <c r="C2">
-        <v>0.3714285714285714</v>
+        <v>0.4366197183098591</v>
       </c>
       <c r="D2">
-        <v>0.8224299065420561</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F2">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3488372093023256</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="B2">
-        <v>0.01886792452830189</v>
+        <v>0.01754385964912281</v>
       </c>
       <c r="C2">
-        <v>0.4366197183098591</v>
+        <v>0.4225352112676056</v>
       </c>
       <c r="D2">
-        <v>0.8333333333333334</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
